--- a/docs/リグレッション試験項目書.xlsx
+++ b/docs/リグレッション試験項目書.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c10e673dbabcf598/デスクトップ/x/待機用成果物/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{A2B66D83-8B11-44DF-971E-33E1A9F09D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1223DDB1-BF41-40C1-875D-D914479B96C7}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{A2B66D83-8B11-44DF-971E-33E1A9F09D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29173348-F4D4-4DE3-B982-8158FFCA5524}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{DEF1F26A-6267-4A97-B0EE-0C93CABC89FA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{DEF1F26A-6267-4A97-B0EE-0C93CABC89FA}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDo" sheetId="1" r:id="rId1"/>
     <sheet name="Swag Labs" sheetId="2" r:id="rId2"/>
+    <sheet name="API" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="217">
   <si>
     <t>No</t>
   </si>
@@ -550,13 +551,145 @@
   <si>
     <t>5. 注文完了（Complete）</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>API-01</t>
+  </si>
+  <si>
+    <t>ユーザー情報取得</t>
+  </si>
+  <si>
+    <t>APIが利用可能な状態</t>
+  </si>
+  <si>
+    <t>GET /api/users/2 を実行</t>
+  </si>
+  <si>
+    <t>ステータスコード200が返却される</t>
+  </si>
+  <si>
+    <t>API-02</t>
+  </si>
+  <si>
+    <t>id=2のユーザー情報が返却される</t>
+  </si>
+  <si>
+    <t>API-03</t>
+  </si>
+  <si>
+    <t>存在しないユーザー取得</t>
+  </si>
+  <si>
+    <t>GET /api/users/999 を実行</t>
+  </si>
+  <si>
+    <t>ステータスコード404が返却される</t>
+  </si>
+  <si>
+    <t>API-04</t>
+  </si>
+  <si>
+    <t>ユーザー一覧取得</t>
+  </si>
+  <si>
+    <t>GET /api/users?page=1 を実行</t>
+  </si>
+  <si>
+    <t>API-05</t>
+  </si>
+  <si>
+    <t>ユーザー一覧が1件以上返却される</t>
+  </si>
+  <si>
+    <t>API-06</t>
+  </si>
+  <si>
+    <t>ユーザー作成</t>
+  </si>
+  <si>
+    <t>name=shuya、job=qaでPOST /api/users を実行</t>
+  </si>
+  <si>
+    <t>ステータスコード201が返却される</t>
+  </si>
+  <si>
+    <t>API-07</t>
+  </si>
+  <si>
+    <t>入力したnameとjobが返却される</t>
+  </si>
+  <si>
+    <t>API-08</t>
+  </si>
+  <si>
+    <t>作成日時(createdAt)が返却される</t>
+  </si>
+  <si>
+    <t>API-09</t>
+  </si>
+  <si>
+    <t>ユーザー更新</t>
+  </si>
+  <si>
+    <t>PUT /api/users/2 を実行</t>
+  </si>
+  <si>
+    <t>API-10</t>
+  </si>
+  <si>
+    <t>name=shuya、job=lead qaでPUT /api/users/2 を実行</t>
+  </si>
+  <si>
+    <t>更新内容が返却される</t>
+  </si>
+  <si>
+    <t>API-11</t>
+  </si>
+  <si>
+    <t>ユーザー削除</t>
+  </si>
+  <si>
+    <t>DELETE /api/users/2 を実行</t>
+  </si>
+  <si>
+    <t>ステータスコード204が返却される</t>
+  </si>
+  <si>
+    <t>API-12</t>
+  </si>
+  <si>
+    <t>レスポンスボディが空であること</t>
+  </si>
+  <si>
+    <t>API-13</t>
+  </si>
+  <si>
+    <t>レスポンス形式確認</t>
+  </si>
+  <si>
+    <t>dataオブジェクトが存在する</t>
+  </si>
+  <si>
+    <t>API-14</t>
+  </si>
+  <si>
+    <t>id、email、first_name、last_nameが含まれる</t>
+  </si>
+  <si>
+    <t>API-15</t>
+  </si>
+  <si>
+    <t>Content-Type確認</t>
+  </si>
+  <si>
+    <t>Content-Typeがapplication/jsonである</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,13 +722,32 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -627,7 +779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -644,6 +796,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1476,7 +1634,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>69</v>
       </c>
@@ -1493,7 +1651,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
         <v>73</v>
       </c>
@@ -1510,7 +1668,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
         <v>76</v>
       </c>
@@ -1847,7 +2005,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
         <v>135</v>
       </c>
@@ -1864,7 +2022,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
         <v>139</v>
       </c>
@@ -1881,7 +2039,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
         <v>142</v>
       </c>
@@ -2037,4 +2195,293 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD5C709-78BB-42A0-A939-E32E1C17A09A}">
+  <dimension ref="A3:E18"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="46.75" customWidth="1"/>
+    <col min="5" max="5" width="51.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/リグレッション試験項目書.xlsx
+++ b/docs/リグレッション試験項目書.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c10e673dbabcf598/デスクトップ/x/待機用成果物/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{A2B66D83-8B11-44DF-971E-33E1A9F09D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29173348-F4D4-4DE3-B982-8158FFCA5524}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{A2B66D83-8B11-44DF-971E-33E1A9F09D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5F574E9-1CB7-4190-80A7-7A808F041DFD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{DEF1F26A-6267-4A97-B0EE-0C93CABC89FA}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDo" sheetId="1" r:id="rId1"/>
     <sheet name="Swag Labs" sheetId="2" r:id="rId2"/>
-    <sheet name="API" sheetId="3" r:id="rId3"/>
+    <sheet name="DummyJSON" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="216">
   <si>
     <t>No</t>
   </si>
@@ -556,133 +556,130 @@
     <t>API-01</t>
   </si>
   <si>
-    <t>ユーザー情報取得</t>
-  </si>
-  <si>
-    <t>APIが利用可能な状態</t>
-  </si>
-  <si>
-    <t>GET /api/users/2 を実行</t>
-  </si>
-  <si>
     <t>ステータスコード200が返却される</t>
   </si>
   <si>
     <t>API-02</t>
   </si>
   <si>
-    <t>id=2のユーザー情報が返却される</t>
-  </si>
-  <si>
     <t>API-03</t>
   </si>
   <si>
-    <t>存在しないユーザー取得</t>
-  </si>
-  <si>
-    <t>GET /api/users/999 を実行</t>
-  </si>
-  <si>
     <t>ステータスコード404が返却される</t>
   </si>
   <si>
     <t>API-04</t>
   </si>
   <si>
-    <t>ユーザー一覧取得</t>
-  </si>
-  <si>
-    <t>GET /api/users?page=1 を実行</t>
-  </si>
-  <si>
     <t>API-05</t>
   </si>
   <si>
-    <t>ユーザー一覧が1件以上返却される</t>
-  </si>
-  <si>
     <t>API-06</t>
   </si>
   <si>
-    <t>ユーザー作成</t>
-  </si>
-  <si>
-    <t>name=shuya、job=qaでPOST /api/users を実行</t>
-  </si>
-  <si>
-    <t>ステータスコード201が返却される</t>
-  </si>
-  <si>
     <t>API-07</t>
   </si>
   <si>
-    <t>入力したnameとjobが返却される</t>
-  </si>
-  <si>
     <t>API-08</t>
   </si>
   <si>
-    <t>作成日時(createdAt)が返却される</t>
-  </si>
-  <si>
     <t>API-09</t>
   </si>
   <si>
-    <t>ユーザー更新</t>
-  </si>
-  <si>
-    <t>PUT /api/users/2 を実行</t>
-  </si>
-  <si>
     <t>API-10</t>
   </si>
   <si>
-    <t>name=shuya、job=lead qaでPUT /api/users/2 を実行</t>
-  </si>
-  <si>
     <t>更新内容が返却される</t>
   </si>
   <si>
     <t>API-11</t>
   </si>
   <si>
-    <t>ユーザー削除</t>
-  </si>
-  <si>
-    <t>DELETE /api/users/2 を実行</t>
-  </si>
-  <si>
-    <t>ステータスコード204が返却される</t>
-  </si>
-  <si>
     <t>API-12</t>
   </si>
   <si>
-    <t>レスポンスボディが空であること</t>
-  </si>
-  <si>
     <t>API-13</t>
   </si>
   <si>
     <t>レスポンス形式確認</t>
   </si>
   <si>
-    <t>dataオブジェクトが存在する</t>
-  </si>
-  <si>
     <t>API-14</t>
   </si>
   <si>
-    <t>id、email、first_name、last_nameが含まれる</t>
-  </si>
-  <si>
     <t>API-15</t>
   </si>
   <si>
     <t>Content-Type確認</t>
   </si>
   <si>
-    <t>Content-Typeがapplication/jsonである</t>
+    <t>商品一覧取得</t>
+  </si>
+  <si>
+    <t>API利用可能</t>
+  </si>
+  <si>
+    <t>GET /products</t>
+  </si>
+  <si>
+    <t>商品一覧が1件以上返却される</t>
+  </si>
+  <si>
+    <t>商品詳細取得</t>
+  </si>
+  <si>
+    <t>GET /products/1</t>
+  </si>
+  <si>
+    <t>商品ID=1が返却される</t>
+  </si>
+  <si>
+    <t>存在しない商品取得</t>
+  </si>
+  <si>
+    <t>GET /products/999999</t>
+  </si>
+  <si>
+    <t>ユーザー取得</t>
+  </si>
+  <si>
+    <t>GET /users/1</t>
+  </si>
+  <si>
+    <t>ユーザーID=1が返却される</t>
+  </si>
+  <si>
+    <t>カート取得</t>
+  </si>
+  <si>
+    <t>GET /carts/1</t>
+  </si>
+  <si>
+    <t>カート内商品が返却される</t>
+  </si>
+  <si>
+    <t>商品登録</t>
+  </si>
+  <si>
+    <t>POST /products を実行</t>
+  </si>
+  <si>
+    <t>ステータスコード201または200が返却される</t>
+  </si>
+  <si>
+    <t>商品名が返却される</t>
+  </si>
+  <si>
+    <t>商品更新</t>
+  </si>
+  <si>
+    <t>PUT /products/1 を実行</t>
+  </si>
+  <si>
+    <t>id、title、priceが含まれる</t>
+  </si>
+  <si>
+    <t>application/jsonが返却される</t>
   </si>
 </sst>
 </file>
@@ -2230,254 +2227,254 @@
         <v>173</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="D11" s="7" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="33" x14ac:dyDescent="0.55000000000000004">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="7" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>
